--- a/files/subjectassign.xlsx
+++ b/files/subjectassign.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5703125" bestFit="1" customWidth="1" min="1" max="8"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PRF-2026-010</t>
+          <t>PRF-2026-004</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PRF-2026-010</t>
+          <t>PRF-2026-005</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PRF-2026-010</t>
+          <t>PRF-2026-006</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PRF-2026-006</t>
+          <t>PRF-2026-004</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PRF-2026-006</t>
+          <t>PRF-2026-005</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2/1</t>
+          <t>3/1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PRF-2026-007</t>
+          <t>PRF-2026-004</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2/1</t>
+          <t>3/1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PRF-2026-007</t>
+          <t>PRF-2026-005</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2/1</t>
+          <t>3/1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PRF-2026-007</t>
+          <t>PRF-2026-006</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PRF-2026-008</t>
+          <t>PRF-2026-004</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PRF-2026-008</t>
+          <t>PRF-2026-005</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PRF-2026-008</t>
+          <t>PRF-2026-006</t>
         </is>
       </c>
     </row>
@@ -907,32 +907,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ics</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAIS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AET101</t>
+          <t>AIS101</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PRF-2026-011</t>
+          <t>PRF-2026-002</t>
         </is>
       </c>
     </row>
@@ -944,32 +944,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ics</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAIS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AET102</t>
+          <t>ACC102</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PRF-2026-011</t>
+          <t>PRF-2026-015</t>
         </is>
       </c>
     </row>
@@ -981,32 +981,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ics</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAIS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AET201</t>
+          <t>IT103</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PRF-2026-011</t>
+          <t>PRF-2026-022</t>
         </is>
       </c>
     </row>
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ics</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAIS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AET101</t>
+          <t>AIS101</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>4/1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PRF-2026-012</t>
+          <t>PRF-2026-002</t>
         </is>
       </c>
     </row>
@@ -1055,32 +1055,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ics</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAIS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AET102</t>
+          <t>ACC102</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>4/1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PRF-2026-012</t>
+          <t>PRF-2026-015</t>
         </is>
       </c>
     </row>
@@ -1092,32 +1092,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ics</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAIS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AET201</t>
+          <t>IT103</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>4/1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PRF-2026-012</t>
+          <t>PRF-2026-022</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PRF-2026-004</t>
+          <t>PRF-2026-018</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PRF-2026-004</t>
+          <t>PRF-2026-025</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PRF-2026-004</t>
+          <t>PRF-2026-018</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4/2</t>
+          <t>2/1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PRF-2026-005</t>
+          <t>PRF-2026-018</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4/2</t>
+          <t>2/1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PRF-2026-005</t>
+          <t>PRF-2026-025</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BSAET</t>
+          <t>BSAMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4/2</t>
+          <t>2/1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PRF-2026-005</t>
+          <t>PRF-2026-018</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AMT101</t>
+          <t>AET101</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AMT102</t>
+          <t>AET102</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PRF-2026-018</t>
+          <t>PRF-2026-025</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AMT201</t>
+          <t>AET201</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1462,32 +1462,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AMT101</t>
+          <t>AVT101</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PRF-2026-055</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1499,32 +1499,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AMT102</t>
+          <t>THC102</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PRF-2026-055</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AMT201</t>
+          <t>AVT201</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PRF-2026-055</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1573,22 +1573,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AMT101</t>
+          <t>AVT101</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PRF-2026-035</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1610,22 +1610,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AMT102</t>
+          <t>THC102</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PRF-2026-035</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AMT201</t>
+          <t>AVT201</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PRF-2026-035</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1684,22 +1684,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AMT101</t>
+          <t>AVT101</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PRF-2026-065</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1721,22 +1721,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AMT102</t>
+          <t>THC102</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PRF-2026-065</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1758,22 +1758,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AMT201</t>
+          <t>AVT201</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PRF-2026-065</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1795,32 +1795,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AMT101</t>
+          <t>AVT101</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>4/1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PRF-2026-025</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1832,32 +1832,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AMT102</t>
+          <t>THC102</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>4/1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PRF-2026-025</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1869,32 +1869,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>mactan</t>
+          <t>villamor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>inet</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BSAMT</t>
+          <t>BSAVCOMM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AMT201</t>
+          <t>AVT201</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>4/1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PRF-2026-025</t>
+          <t>PRF-2026-003</t>
         </is>
       </c>
     </row>
@@ -1911,27 +1911,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ics</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSAVTOUR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ACC102</t>
+          <t>AVT101</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PRF-2026-015</t>
+          <t>PRF-2026-001</t>
         </is>
       </c>
     </row>
@@ -1948,27 +1948,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ics</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSAVTOUR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AIS101</t>
+          <t>THC102</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PRF-2026-015</t>
+          <t>PRF-2026-016</t>
         </is>
       </c>
     </row>
@@ -1985,27 +1985,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ics</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSAVTOUR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IT103</t>
+          <t>AVT201</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PRF-2026-015</t>
+          <t>PRF-2026-023</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ics</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSAVTOUR</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ACC102</t>
+          <t>AVT101</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PRF-2026-062</t>
+          <t>PRF-2026-001</t>
         </is>
       </c>
     </row>
@@ -2059,17 +2059,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ics</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSAVTOUR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AIS101</t>
+          <t>THC102</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PRF-2026-062</t>
+          <t>PRF-2026-016</t>
         </is>
       </c>
     </row>
@@ -2096,17 +2096,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ics</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSAVTOUR</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IT103</t>
+          <t>AVT201</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PRF-2026-062</t>
+          <t>PRF-2026-023</t>
         </is>
       </c>
     </row>
@@ -2133,17 +2133,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ics</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSAVTOUR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ACC102</t>
+          <t>AVT101</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PRF-2026-022</t>
+          <t>PRF-2026-001</t>
         </is>
       </c>
     </row>
@@ -2170,17 +2170,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ics</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSAVTOUR</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AIS101</t>
+          <t>THC102</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PRF-2026-022</t>
+          <t>PRF-2026-016</t>
         </is>
       </c>
     </row>
@@ -2207,17 +2207,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ics</t>
+          <t>ilas</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSAVTOUR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IT103</t>
+          <t>AVT201</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PRF-2026-022</t>
+          <t>PRF-2026-023</t>
         </is>
       </c>
     </row>
@@ -2249,22 +2249,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSIT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ACC102</t>
+          <t>AIS101</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PRF-2026-002</t>
+          <t>PRF-2026-014</t>
         </is>
       </c>
     </row>
@@ -2286,22 +2286,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSIT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AIS101</t>
+          <t>ACC102</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PRF-2026-002</t>
+          <t>PRF-2026-017</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BSAIS</t>
+          <t>BSIT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PRF-2026-002</t>
+          <t>PRF-2026-014</t>
         </is>
       </c>
     </row>
@@ -2365,17 +2365,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IT101</t>
+          <t>AIS101</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PRF-2026-082</t>
+          <t>PRF-2026-014</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IT102</t>
+          <t>ACC102</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PRF-2026-082</t>
+          <t>PRF-2026-017</t>
         </is>
       </c>
     </row>
@@ -2439,1904 +2439,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IT201</t>
+          <t>IT103</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PRF-2026-082</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>IT101</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>PRF-2026-017</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>IT102</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>PRF-2026-017</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>IT201</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>PRF-2026-017</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>IT101</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2/1</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>PRF-2026-032</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>IT102</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2/1</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>PRF-2026-032</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>IT201</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2/1</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>PRF-2026-032</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>IT101</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>PRF-2026-036</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>IT102</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>PRF-2026-036</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>IT201</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>PRF-2026-036</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>IT101</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>3/1</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>PRF-2026-076</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>IT102</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>3/1</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>PRF-2026-076</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>IT201</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>3/1</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>PRF-2026-076</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>IT101</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>3/2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
           <t>PRF-2026-014</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>IT102</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>3/2</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>PRF-2026-014</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>IT201</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>3/2</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>PRF-2026-014</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>IT101</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>4/2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>PRF-2026-056</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>IT102</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>4/2</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>PRF-2026-056</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ics</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>BSIT</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>IT201</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>4/2</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>PRF-2026-056</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>BSAVComm</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AVC101</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>PRF-2026-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>BSAVComm</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AVC201</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>PRF-2026-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>BSAVComm</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>ENG102</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>PRF-2026-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>BSAVComm</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AVC101</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>PRF-2026-101</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>BSAVComm</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AVC201</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>PRF-2026-101</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>BSAVComm</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>ENG102</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>PRF-2026-101</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>BSAVComm</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AVC101</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2/1</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>PRF-2026-043</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>BSAVComm</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AVC201</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2/1</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>PRF-2026-043</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>BSAVComm</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>ENG102</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2/1</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>PRF-2026-043</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AVT101</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>PRF-2026-016</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AVT201</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>PRF-2026-016</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>THC102</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>PRF-2026-016</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AVT101</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>PRF-2026-037</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AVT201</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>PRF-2026-037</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>THC102</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>PRF-2026-037</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AVT101</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2/1</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>PRF-2026-097</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AVT201</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2/1</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>PRF-2026-097</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>THC102</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2/1</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>PRF-2026-097</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AVT101</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>PRF-2026-033</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AVT201</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>PRF-2026-033</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>THC102</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>PRF-2026-033</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AVT101</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>3/1</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>PRF-2026-023</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AVT201</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>3/1</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>PRF-2026-023</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>THC102</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>3/1</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>PRF-2026-023</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AVT101</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>3/2</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>PRF-2026-027</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AVT201</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>3/2</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>PRF-2026-027</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>THC102</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>3/2</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>PRF-2026-027</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AVT101</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>4/1</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>PRF-2026-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AVT201</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>4/1</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>PRF-2026-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>THC102</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>4/1</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>PRF-2026-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AVT101</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>4/2</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>PRF-2026-046</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AVT201</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>4/2</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>PRF-2026-046</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>villamor</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>ilas</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>BSAVTour</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>THC102</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>4/2</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>PRF-2026-046</t>
         </is>
       </c>
     </row>

--- a/files/subjectassign.xlsx
+++ b/files/subjectassign.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="45" yWindow="300" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -456,11 +456,6 @@
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -493,11 +488,6 @@
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -530,11 +520,6 @@
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -567,11 +552,6 @@
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -604,11 +584,6 @@
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -641,11 +616,6 @@
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -678,11 +648,6 @@
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -715,11 +680,6 @@
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -752,11 +712,6 @@
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -789,11 +744,6 @@
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -826,11 +776,6 @@
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -863,11 +808,6 @@
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -900,11 +840,6 @@
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -937,11 +872,6 @@
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -974,11 +904,6 @@
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1011,11 +936,6 @@
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1048,11 +968,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1085,11 +1000,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1122,11 +1032,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -1159,11 +1064,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -1196,11 +1096,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -1233,11 +1128,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -1270,11 +1160,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -1307,11 +1192,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -1344,11 +1224,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -1381,11 +1256,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -1418,11 +1288,6 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>mactan</t>
@@ -1455,11 +1320,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1492,11 +1352,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1529,11 +1384,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1566,11 +1416,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1603,11 +1448,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1640,11 +1480,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1677,11 +1512,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1714,11 +1544,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1751,11 +1576,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1788,11 +1608,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1825,11 +1640,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1862,11 +1672,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1899,11 +1704,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1931,16 +1731,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PRF-2026-001</t>
+          <t xml:space="preserve">professor </t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -1973,11 +1768,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2010,11 +1800,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2042,16 +1827,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PRF-2026-001</t>
+          <t xml:space="preserve">professor </t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2084,11 +1864,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2121,11 +1896,6 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2153,16 +1923,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PRF-2026-001</t>
+          <t>professor</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2195,11 +1960,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2232,11 +1992,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2269,11 +2024,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2306,11 +2056,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2343,11 +2088,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2380,11 +2120,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>villamor</t>
@@ -2417,11 +2152,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2nd-semester-2025-2026</t>
-        </is>
-      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>villamor</t>
